--- a/attendance_data.xlsx
+++ b/attendance_data.xlsx
@@ -1,38 +1,72 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AuditData" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Credentials" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00365F91"/>
+        <bgColor rgb="00365F91"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F5F8"/>
+        <bgColor rgb="00F2F5F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -40,18 +74,120 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -130,7 +266,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -165,7 +300,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -341,10 +475,299 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>serviceDate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>timeIn</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>timeOut</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>serviceFormId</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>optionCode</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>12:11 AM</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>12:15 PM</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>BS-MIRNY-Q6P4N5XGUMULE</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Normal Bulk Entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>BS-MIRNY-Q6P4N5XGUMULE</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Full Day Session</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>10:30 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>11:30 AM</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>BS-MIRNY-Q6P4N5XGUMULE</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Short Session Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>02:00 PM</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>01:00 PM</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>BS-MIRNY-Q6P4N5XGUMULE</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Time Clash Failure Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>05/12/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>11:00 PM</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>11:30 PM</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>BS-MIRNY-Q6P4N5XGUMULE</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Late Night Logging</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>loginName</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>providerCode</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>mirza</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>MIR-NY</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>therap321#</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/attendance_data.xlsx
+++ b/attendance_data.xlsx
@@ -570,7 +570,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3">
-        <v>46049</v>
+        <v>46052</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>28</v>

--- a/attendance_data.xlsx
+++ b/attendance_data.xlsx
@@ -570,7 +570,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3">
-        <v>46052</v>
+        <v>46180</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>28</v>

--- a/attendance_data.xlsx
+++ b/attendance_data.xlsx
@@ -539,7 +539,7 @@
     <col min="1" max="1" style="10" width="22.005" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="11" width="22.005" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="11" width="22.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="13" width="25.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="13" width="42.005" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="11" width="22.005" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="11" width="22.005" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="13" width="22.005" customWidth="1" bestFit="1"/>
@@ -570,7 +570,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3">
-        <v>46180</v>
+        <v>46183</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>28</v>

--- a/attendance_data.xlsx
+++ b/attendance_data.xlsx
@@ -570,7 +570,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>28</v>

--- a/attendance_data.xlsx
+++ b/attendance_data.xlsx
@@ -570,7 +570,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>28</v>

--- a/attendance_data.xlsx
+++ b/attendance_data.xlsx
@@ -34,10 +34,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
-    <numFmt numFmtId="165" formatCode="h:mm Am/Pm"/>
+    <numFmt numFmtId="164" formatCode="h:mm\ \t\t"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -401,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,14 +426,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>07/03/2026</v>
+      <c r="A2">
+        <v>46043</v>
       </c>
       <c r="B2" t="str">
-        <v>12:11 AM</v>
+        <v>09:00 AM</v>
       </c>
       <c r="C2" t="str">
-        <v>12:15 PM</v>
+        <v>05:00 PM</v>
       </c>
       <c r="D2" t="str">
         <v>BS-MIRNY-Q6P4N5XGUMULE</v>
@@ -446,12 +445,35 @@
         <v>APPROVED</v>
       </c>
       <c r="G2" t="str">
-        <v>Normal Bulk Entry</v>
+        <v>Full Day Session</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>46044</v>
+      </c>
+      <c r="B3" t="str">
+        <v>10:30 AM</v>
+      </c>
+      <c r="C3" t="str">
+        <v>11:30 AM</v>
+      </c>
+      <c r="D3" t="str">
+        <v>BS-MIRNY-Q6P4N5XGUMULE</v>
+      </c>
+      <c r="E3" t="str">
+        <v>P</v>
+      </c>
+      <c r="F3" t="str">
+        <v>APPROVED</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Short Session Check</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -733,8 +755,23 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="str">
+        <v>04/21/26'</v>
+      </c>
       <c r="B12" t="str">
         <v>11:00 PM</v>
+      </c>
+      <c r="C12">
+        <v>5.972453703703704</v>
+      </c>
+      <c r="D12" t="str">
+        <v>BS-MIRNY-Q6P4N5XGUMULE</v>
+      </c>
+      <c r="E12" t="str">
+        <v>P</v>
+      </c>
+      <c r="F12" t="str">
+        <v>APPROVED</v>
       </c>
     </row>
   </sheetData>

--- a/attendance_data.xlsx
+++ b/attendance_data.xlsx
@@ -34,9 +34,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="h:mm\ \t\t"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -426,8 +425,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>46043</v>
+      <c r="A2" t="str">
+        <v>01/17/2026</v>
       </c>
       <c r="B2" t="str">
         <v>09:00 AM</v>
@@ -449,8 +448,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>46044</v>
+      <c r="A3" t="str">
+        <v>01/18/2026</v>
       </c>
       <c r="B3" t="str">
         <v>10:30 AM</v>

--- a/attendance_data.xlsx
+++ b/attendance_data.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -426,13 +426,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>01/17/2026</v>
+        <v>03/15/2026</v>
       </c>
       <c r="B2" t="str">
-        <v>09:00 AM</v>
+        <v>10:30 AM</v>
       </c>
       <c r="C2" t="str">
-        <v>05:00 PM</v>
+        <v>10:30 AM</v>
       </c>
       <c r="D2" t="str">
         <v>BS-MIRNY-Q6P4N5XGUMULE</v>
@@ -449,13 +449,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>01/18/2026</v>
+        <v>03/16/2026</v>
       </c>
       <c r="B3" t="str">
         <v>10:30 AM</v>
       </c>
       <c r="C3" t="str">
-        <v>11:30 AM</v>
+        <v>10:30 AM</v>
       </c>
       <c r="D3" t="str">
         <v>BS-MIRNY-Q6P4N5XGUMULE</v>
@@ -470,9 +470,129 @@
         <v>Short Session Check</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>03/17/2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>10:30 AM</v>
+      </c>
+      <c r="C4" t="str">
+        <v>10:30 AM</v>
+      </c>
+      <c r="D4" t="str">
+        <v>BS-MIRNY-Q6P4N5XGUMULE</v>
+      </c>
+      <c r="E4" t="str">
+        <v>P</v>
+      </c>
+      <c r="F4" t="str">
+        <v>APPROVED</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Short Session Check</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>03/18/2026</v>
+      </c>
+      <c r="B5" t="str">
+        <v>10:30 AM</v>
+      </c>
+      <c r="C5" t="str">
+        <v>10:30 AM</v>
+      </c>
+      <c r="D5" t="str">
+        <v>BS-MIRNY-Q6P4N5XGUMULE</v>
+      </c>
+      <c r="E5" t="str">
+        <v>P</v>
+      </c>
+      <c r="F5" t="str">
+        <v>APPROVED</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Short Session Check</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>03/19/2026</v>
+      </c>
+      <c r="B6" t="str">
+        <v>10:30 AM</v>
+      </c>
+      <c r="C6" t="str">
+        <v>10:30 AM</v>
+      </c>
+      <c r="D6" t="str">
+        <v>BS-MIRNY-Q6P4N5XGUMULE</v>
+      </c>
+      <c r="E6" t="str">
+        <v>P</v>
+      </c>
+      <c r="F6" t="str">
+        <v>APPROVED</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Short Session Check</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>03/20/2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>10:30 AM</v>
+      </c>
+      <c r="C7" t="str">
+        <v>10:30 AM</v>
+      </c>
+      <c r="D7" t="str">
+        <v>BS-MIRNY-Q6P4N5XGUMULE</v>
+      </c>
+      <c r="E7" t="str">
+        <v>P</v>
+      </c>
+      <c r="F7" t="str">
+        <v>APPROVED</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Short Session Check</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>03/21/2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>10:30 AM</v>
+      </c>
+      <c r="C8" t="str">
+        <v>10:30 AM</v>
+      </c>
+      <c r="D8" t="str">
+        <v>BS-MIRNY-Q6P4N5XGUMULE</v>
+      </c>
+      <c r="E8" t="str">
+        <v>P</v>
+      </c>
+      <c r="F8" t="str">
+        <v>APPROVED</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Short Session Check</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>03/21/2027</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G9"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -540,7 +660,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>46039</v>
+        <v>46133</v>
       </c>
       <c r="B2" t="str">
         <v>09:00 AM</v>
@@ -563,7 +683,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>46040</v>
+        <v>46134</v>
       </c>
       <c r="B3" t="str">
         <v>10:30 AM</v>
@@ -586,7 +706,7 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>46041</v>
+        <v>46135</v>
       </c>
       <c r="B4" t="str">
         <v>02:00 PM</v>
@@ -609,7 +729,7 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>46042</v>
+        <v>46136</v>
       </c>
       <c r="B5" t="str">
         <v>11:00 PM</v>
@@ -632,7 +752,7 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>46043</v>
+        <v>46137</v>
       </c>
       <c r="D6" t="str">
         <v>BS-MIRNY-Q6P4N5XGUMULE</v>
@@ -646,7 +766,7 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>46044</v>
+        <v>46138</v>
       </c>
       <c r="B7" t="str">
         <v>11:00 PM</v>
@@ -669,7 +789,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>46045</v>
+        <v>46139</v>
       </c>
       <c r="B8" t="str">
         <v>11:00 PM</v>
@@ -689,7 +809,7 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>46046</v>
+        <v>46140</v>
       </c>
       <c r="B9" t="str">
         <v>11:00 PM</v>
@@ -712,7 +832,7 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>46047</v>
+        <v>46141</v>
       </c>
       <c r="B10" t="str">
         <v>11:00 PM</v>
@@ -735,7 +855,7 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>46048</v>
+        <v>46142</v>
       </c>
       <c r="B11" t="str">
         <v>11:00 PM</v>
@@ -754,8 +874,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>04/21/26'</v>
+      <c r="A12">
+        <v>46143</v>
       </c>
       <c r="B12" t="str">
         <v>11:00 PM</v>

--- a/attendance_data.xlsx
+++ b/attendance_data.xlsx
@@ -426,7 +426,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>03/15/2026</v>
+        <v>03/23/2026</v>
       </c>
       <c r="B2" t="str">
         <v>10:30 AM</v>
@@ -449,7 +449,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>03/16/2026</v>
+        <v>03/24/2026</v>
       </c>
       <c r="B3" t="str">
         <v>10:30 AM</v>
@@ -472,7 +472,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>03/17/2026</v>
+        <v>03/25/2026</v>
       </c>
       <c r="B4" t="str">
         <v>10:30 AM</v>
@@ -495,7 +495,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>03/18/2026</v>
+        <v>03/26/2026</v>
       </c>
       <c r="B5" t="str">
         <v>10:30 AM</v>
@@ -518,7 +518,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>03/19/2026</v>
+        <v>03/27/2026</v>
       </c>
       <c r="B6" t="str">
         <v>10:30 AM</v>
@@ -541,7 +541,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>03/20/2026</v>
+        <v>03/28/2026</v>
       </c>
       <c r="B7" t="str">
         <v>10:30 AM</v>
@@ -564,7 +564,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>03/21/2026</v>
+        <v>03/29/2026</v>
       </c>
       <c r="B8" t="str">
         <v>10:30 AM</v>
@@ -587,7 +587,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>03/21/2027</v>
+        <v>03/29/2027</v>
       </c>
     </row>
   </sheetData>
